--- a/Roguelike-Deckbuilder/Assets/Config/Excel/EnemyConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/EnemyConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920A02BB-D974-4AD2-8536-3B22E0B432D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142541EF-2036-4FDB-BC62-6A5AF8DCB2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4908" yWindow="4440" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyConfig" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>Twig_slime_s</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -142,6 +142,18 @@
   </si>
   <si>
     <t>[8,9,10,11]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BygoneEffigy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旧日雕像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[12,13,14]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -850,12 +862,24 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="1">
+        <v>127</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
